--- a/docs/design/ACSMS-SCR-021/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_配達手数料支払情報出力画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-021/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_配達手数料支払情報出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,20 +1363,144 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>「手数料」列を配達手数料単価から振込手数料負担区分（TESURYO_KUBUN ラベル）表示に変更</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="18" t="inlineStr"/>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="20" t="inlineStr">
+        <is>
+          <t>実装との差分補完：カテゴリ6を新設し2件追加（TC-041〜042）。041＝集計対象を紙版(dokusya_shubetsu=1)のみに限定し電子版・併読を除外する条件（顧客要件2026-08 / #56599・API設計書 v1.3）。042＝失効した配達手数料単価(`active_flg=false`)を参照する販売店が居る場合の出力ブロック（HTTP 409 `INACTIVE_TANKA_REFERENCED`・`errors[]` 先頭15件打ち切りと `total`・プレビューと出力の両方でチェック・API設計書 v1.2）。いずれも本書 v1.1（2026/07/02）より後に入った仕様で未反映だった</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="19" t="inlineStr"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="11" t="n"/>
+      <c r="AC4" s="19" t="inlineStr"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="24">
+    <mergeCell ref="O3:V3"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="W3:AB3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC4:AH4"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC2:AH2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="W4:AB4"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="AC2:AH2"/>
-    <mergeCell ref="AC1:AH1"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="O1:V1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6239,7 +6363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ56"/>
+  <dimension ref="A1:BQ59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9050,7 +9174,7 @@
       <c r="BP24" s="10" t="n"/>
       <c r="BQ24" s="11" t="n"/>
     </row>
-    <row r="25" ht="208" customHeight="1">
+    <row r="25" ht="320" customHeight="1">
       <c r="A25" s="44" t="n">
         <v>12</v>
       </c>
@@ -9158,7 +9282,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・対象月・販売店コード・販売店名・当月部数・当月金額・支払サイクル・金融機関コード・金融機関名・口座支店コード・口座支店名・貯金種目・口座番号・口座名義・備考の各列が表示されること
+            <t xml:space="preserve">・対象月・販売店コード・販売店名・当月部数・当月金額・支払サイクル・金融機関コード・金融機関名・口座支店コード・口座支店名・貯金種目・口座番号・口座名義・手数料・備考の各列が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「手数料」列には振込手数料負担区分（m_hanbaiten.furikomi_tesuryo_futan_kubun）が m_code TESURYO_KUBUN のラベル（1:JA / 2:販売店）で表示され、金額（¥単価）が表示されないこと
 </t>
           </r>
           <r>
@@ -11885,7 +12017,7 @@
       <c r="BP43" s="10" t="n"/>
       <c r="BQ43" s="11" t="n"/>
     </row>
-    <row r="44" ht="256" customHeight="1">
+    <row r="44" ht="368" customHeight="1">
       <c r="A44" s="44" t="n">
         <v>29</v>
       </c>
@@ -12001,7 +12133,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・ヘッダ行に対象月・販売店コード・販売店名・当月部数・当月金額・支払サイクル・金融機関コード・金融機関名・口座支店コード・口座支店名・貯金種目・口座番号・口座名義・備考が表示されること
+            <t xml:space="preserve">・ヘッダ行に対象月・販売店コード・販売店名・当月部数・当月金額・支払サイクル・金融機関コード・金融機関名・口座支店コード・口座支店名・貯金種目・口座番号・口座名義・手数料・備考が表示されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・「手数料」列には振込手数料負担区分（m_hanbaiten.furikomi_tesuryo_futan_kubun）が m_code TESURYO_KUBUN のラベル（1:JA / 2:販売店）で出力され、金額（¥単価）が出力されないこと
 </t>
           </r>
           <r>
@@ -14000,11 +14140,768 @@
       <c r="BP56" s="10" t="n"/>
       <c r="BQ56" s="11" t="n"/>
     </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ6: 集計対象の限定・出力ブロック（Scope / Export Gate）</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="10" t="n"/>
+      <c r="AL57" s="10" t="n"/>
+      <c r="AM57" s="10" t="n"/>
+      <c r="AN57" s="10" t="n"/>
+      <c r="AO57" s="10" t="n"/>
+      <c r="AP57" s="10" t="n"/>
+      <c r="AQ57" s="10" t="n"/>
+      <c r="AR57" s="10" t="n"/>
+      <c r="AS57" s="10" t="n"/>
+      <c r="AT57" s="10" t="n"/>
+      <c r="AU57" s="10" t="n"/>
+      <c r="AV57" s="10" t="n"/>
+      <c r="AW57" s="10" t="n"/>
+      <c r="AX57" s="10" t="n"/>
+      <c r="AY57" s="10" t="n"/>
+      <c r="AZ57" s="10" t="n"/>
+      <c r="BA57" s="10" t="n"/>
+      <c r="BB57" s="10" t="n"/>
+      <c r="BC57" s="10" t="n"/>
+      <c r="BD57" s="10" t="n"/>
+      <c r="BE57" s="10" t="n"/>
+      <c r="BF57" s="10" t="n"/>
+      <c r="BG57" s="10" t="n"/>
+      <c r="BH57" s="10" t="n"/>
+      <c r="BI57" s="10" t="n"/>
+      <c r="BJ57" s="10" t="n"/>
+      <c r="BK57" s="10" t="n"/>
+      <c r="BL57" s="10" t="n"/>
+      <c r="BM57" s="10" t="n"/>
+      <c r="BN57" s="10" t="n"/>
+      <c r="BO57" s="10" t="n"/>
+      <c r="BP57" s="10" t="n"/>
+      <c r="BQ57" s="11" t="n"/>
+    </row>
+    <row r="58" ht="450" customHeight="1">
+      <c r="A58" s="44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B58" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-021-041</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="46" t="inlineStr">
+        <is>
+          <t>集計対象 — 紙版のみに限定（#56599）</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`haitatsuryo.export` 権限あり）
+・同一の実在販売店Aに、出力対象年月に配達中の購読者が以下のとおり紐づくこと
+・(a) 紙版（dokusya_shubetsu=1）3件
+・(b) 併読（3）2件
+・(c) 電子版（2）1件（ダミー販売店ではなく実在販売店Aに紐づく状態）
+・ダミー販売店（9999999999）に配達手数料単価が設定されており、電子版購読者が紐づくこと</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="11" t="n"/>
+      <c r="Q58" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力対象年月を指定してプレビューを表示し、販売店Aの部数と金額を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Excelを出力し、販売店Aの行の部数・金額がプレビューと一致することを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ダミー販売店の行がプレビュー・Excelに現れるかを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(b) 併読 と (c) 電子版 だけが紐づく販売店Bで出力する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(b) または (c) の購読者が参照する配達手数料単価を**失効**させてから出力する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="11" t="n"/>
+      <c r="X58" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店Aの部数が **3件分のみ**（紙版のみ）で集計されること。併読2件・電子版1件は加算されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Excelの値がプレビューと一致すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ダミー販売店に配達手数料単価が設定されていても、紐づくのが電子版のみであれば金額が加算されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">販売店Bが 0件（または一覧に現れない）となること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力が**ブロックされないこと**（INACTIVE_TANKA_REFERENCED が発生しないこと）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・配達手数料は「紙を配達した対価」であるため、配達自体が無い電子版(2)と、併読(3)はいずれも対象外（顧客要件2026-08 / #56599）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・従来は購読種別で絞っておらず、実在の販売店に紐づく併読はそのまま加算され、電子版もダミー販売店に配達手数料単価が設定されていれば加算されていた。つまり**マスタの整備状況によって支払金額が変わる**状態だった
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・ステップ5は集計SQLと失効単価チェックSQLの**両方**に同じ購読種別条件が入っていることの確認。片方だけだと「金額は0円なのに失効単価エラーで出力できない」という不整合が起きる
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・口座振替データ出力（SCR-020）は「紙版＋承認済・有料の電子版」で条件が異なる。本画面の条件をそのまま流用しないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="11" t="n"/>
+      <c r="AE58" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF58" s="11" t="n"/>
+      <c r="AG58" s="45" t="inlineStr"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="11" t="n"/>
+      <c r="AJ58" s="45" t="inlineStr"/>
+      <c r="AK58" s="10" t="n"/>
+      <c r="AL58" s="11" t="n"/>
+      <c r="AM58" s="45" t="inlineStr"/>
+      <c r="AN58" s="10" t="n"/>
+      <c r="AO58" s="11" t="n"/>
+      <c r="AP58" s="45" t="inlineStr"/>
+      <c r="AQ58" s="10" t="n"/>
+      <c r="AR58" s="11" t="n"/>
+      <c r="AS58" s="45" t="inlineStr"/>
+      <c r="AT58" s="10" t="n"/>
+      <c r="AU58" s="11" t="n"/>
+      <c r="AV58" s="45" t="inlineStr"/>
+      <c r="AW58" s="10" t="n"/>
+      <c r="AX58" s="11" t="n"/>
+      <c r="AY58" s="45" t="inlineStr"/>
+      <c r="AZ58" s="10" t="n"/>
+      <c r="BA58" s="11" t="n"/>
+      <c r="BB58" s="45" t="inlineStr"/>
+      <c r="BC58" s="10" t="n"/>
+      <c r="BD58" s="11" t="n"/>
+      <c r="BE58" s="45" t="inlineStr"/>
+      <c r="BF58" s="10" t="n"/>
+      <c r="BG58" s="11" t="n"/>
+      <c r="BH58" s="45" t="inlineStr"/>
+      <c r="BI58" s="10" t="n"/>
+      <c r="BJ58" s="11" t="n"/>
+      <c r="BK58" s="46" t="inlineStr"/>
+      <c r="BL58" s="10" t="n"/>
+      <c r="BM58" s="10" t="n"/>
+      <c r="BN58" s="10" t="n"/>
+      <c r="BO58" s="10" t="n"/>
+      <c r="BP58" s="10" t="n"/>
+      <c r="BQ58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="450" customHeight="1">
+      <c r="A59" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-021-042</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>出力ブロック — 失効した配達手数料単価を参照する販売店が存在する場合（INACTIVE_TANKA_REFERENCED）</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`haitatsuryo.export` 権限あり）
+・出力対象の母集合に、配達手数料単価（tanka_type=2）が `active_flg = FALSE` の販売店が 1 件以上存在すること
+・別途、該当が 20 件以上になるパターンも用意すること（打ち切り確認用）</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">失効単価を参照する販売店が1件だけ存在する状態で**プレビュー**を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">同じ状態で**Excel出力**を実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">レスポンスの `error_code`・`message`・`errors[]`・`total` を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">該当が20件存在する状態で実行し、`errors[]` の件数と `total` を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">画面のメッセージ表示と誘導先を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">該当販売店の配達手数料単価を有効な単価へ変更してから再度実行する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>適用期間が出力対象年月から外れているが `active_flg = TRUE` の単価を参照する販売店で出力する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="11" t="n"/>
+      <c r="X59" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">プレビューがブロックされ、HTTPステータスコード409が返ること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力もブロックされ、ファイルが生成されないこと（プレビュー・出力の両方でチェックする）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`error_code: INACTIVE_TANKA_REFERENCED`、`message` が `失効した配達手数料単価を参照している販売店が存在するため、配達手数料支払情報を出力できません。該当販売店の単価を変更してから再度実行してください。` であること。`errors[]` の各要素が `{ field: "&lt;hanbaiten_id&gt;", message: "&lt;販売店コード&gt; &lt;販売店名&gt;（単価: &lt;単価コード&gt; &lt;単価名&gt;）" }` の形であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`errors[]` が**先頭15件で打ち切られる**こと。`total` は 20 のままであること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">「該当 20 件中 15 件を表示」と要約されること。全件の確認・単価変更は**販売店明細検索（失効配達手数料単価参照の絞込）**へ誘導されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力が成功すること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">出力が成功すること（有効判定は `active_flg` のみで行い、適用期間の日付判定はしない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・メッセージは口座振替データ出力（SCR-020）と文言が異なる（「単価」ではなく「配達手数料単価」、対象が「購読者」ではなく「販売店」）。共通の `InactiveTankaReferencedException` に画面別の文言を渡す実装のため、両画面のテストで文言を取り違えないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`errors[].field` は行番号ではなく **`hanbaiten_id`**（SCR-020 は行番号）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・集計対象外の購読者（#56599 で除外される電子版・併読）が参照する失効単価はこのチェックの母集合にも含まれない（ACSMS-TC-021-041 ステップ5 参照）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="11" t="n"/>
+      <c r="AE59" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF59" s="11" t="n"/>
+      <c r="AG59" s="45" t="inlineStr"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="11" t="n"/>
+      <c r="AJ59" s="45" t="inlineStr"/>
+      <c r="AK59" s="10" t="n"/>
+      <c r="AL59" s="11" t="n"/>
+      <c r="AM59" s="45" t="inlineStr"/>
+      <c r="AN59" s="10" t="n"/>
+      <c r="AO59" s="11" t="n"/>
+      <c r="AP59" s="45" t="inlineStr"/>
+      <c r="AQ59" s="10" t="n"/>
+      <c r="AR59" s="11" t="n"/>
+      <c r="AS59" s="45" t="inlineStr"/>
+      <c r="AT59" s="10" t="n"/>
+      <c r="AU59" s="11" t="n"/>
+      <c r="AV59" s="45" t="inlineStr"/>
+      <c r="AW59" s="10" t="n"/>
+      <c r="AX59" s="11" t="n"/>
+      <c r="AY59" s="45" t="inlineStr"/>
+      <c r="AZ59" s="10" t="n"/>
+      <c r="BA59" s="11" t="n"/>
+      <c r="BB59" s="45" t="inlineStr"/>
+      <c r="BC59" s="10" t="n"/>
+      <c r="BD59" s="11" t="n"/>
+      <c r="BE59" s="45" t="inlineStr"/>
+      <c r="BF59" s="10" t="n"/>
+      <c r="BG59" s="11" t="n"/>
+      <c r="BH59" s="45" t="inlineStr"/>
+      <c r="BI59" s="10" t="n"/>
+      <c r="BJ59" s="11" t="n"/>
+      <c r="BK59" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL59" s="10" t="n"/>
+      <c r="BM59" s="10" t="n"/>
+      <c r="BN59" s="10" t="n"/>
+      <c r="BO59" s="10" t="n"/>
+      <c r="BP59" s="10" t="n"/>
+      <c r="BQ59" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="751">
+  <mergeCells count="786">
+    <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
+    <mergeCell ref="BK58:BQ58"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
@@ -14043,6 +14940,7 @@
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
+    <mergeCell ref="E58:I58"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="AJ38:AL38"/>
     <mergeCell ref="BE35:BG35"/>
@@ -14081,7 +14979,9 @@
     <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="BK13:BQ13"/>
+    <mergeCell ref="AM58:AO58"/>
     <mergeCell ref="BE41:BG41"/>
+    <mergeCell ref="Q59:W59"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="BH55:BJ55"/>
@@ -14154,6 +15054,8 @@
     <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
+    <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="B24:D24"/>
@@ -14197,6 +15099,7 @@
     <mergeCell ref="E29:I29"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="B37:D37"/>
+    <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="AE33:AF33"/>
@@ -14231,12 +15134,14 @@
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
+    <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="BK19:BQ19"/>
     <mergeCell ref="X46:AD46"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
+    <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AM31:AO31"/>
@@ -14259,6 +15164,7 @@
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="Q14:W14"/>
+    <mergeCell ref="B59:D59"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="B46:D46"/>
     <mergeCell ref="AS54:AU54"/>
@@ -14327,15 +15233,19 @@
     <mergeCell ref="AE26:AF26"/>
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
+    <mergeCell ref="BB58:BD58"/>
     <mergeCell ref="J47:P47"/>
+    <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
     <mergeCell ref="AP30:AR30"/>
+    <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
     <mergeCell ref="AP46:AR46"/>
+    <mergeCell ref="BK59:BQ59"/>
     <mergeCell ref="BK46:BQ46"/>
     <mergeCell ref="BK40:BQ40"/>
     <mergeCell ref="AE42:AF42"/>
@@ -14380,7 +15290,9 @@
     <mergeCell ref="BH17:BJ17"/>
     <mergeCell ref="E48:I48"/>
     <mergeCell ref="AE47:AF47"/>
+    <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AP11:AR11"/>
@@ -14405,6 +15317,8 @@
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
+    <mergeCell ref="AS58:AU58"/>
+    <mergeCell ref="AV59:AX59"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
     <mergeCell ref="Q31:W31"/>
@@ -14414,13 +15328,16 @@
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="BH37:BJ37"/>
     <mergeCell ref="AE45:AF45"/>
+    <mergeCell ref="X58:AD58"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
+    <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK51:BQ51"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
+    <mergeCell ref="AE59:AF59"/>
     <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="BB41:BD41"/>
     <mergeCell ref="J46:P46"/>
@@ -14503,6 +15420,7 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="Q58:W58"/>
     <mergeCell ref="AV16:AX16"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="Q50:W50"/>
@@ -14515,6 +15433,7 @@
     <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
     <mergeCell ref="AY56:BA56"/>
+    <mergeCell ref="AM59:AO59"/>
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AY43:BA43"/>
@@ -14547,8 +15466,10 @@
     <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
+    <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="BB45:BD45"/>
+    <mergeCell ref="AG58:AI58"/>
     <mergeCell ref="BB32:BD32"/>
     <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
@@ -14562,6 +15483,7 @@
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
+    <mergeCell ref="AJ58:AL58"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -14570,6 +15492,7 @@
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
+    <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
@@ -14592,12 +15515,14 @@
     <mergeCell ref="AV20:AX20"/>
     <mergeCell ref="BE48:BG48"/>
     <mergeCell ref="AS24:AU24"/>
+    <mergeCell ref="A57:BQ57"/>
     <mergeCell ref="AS18:AU18"/>
     <mergeCell ref="AM27:AO27"/>
     <mergeCell ref="BH36:BJ36"/>
     <mergeCell ref="BH11:BJ11"/>
     <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="AJ46:AL46"/>
@@ -14646,6 +15571,7 @@
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E59:I59"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="J15:P15"/>
@@ -14708,6 +15634,7 @@
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
     <mergeCell ref="AJ42:AL42"/>
+    <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
     <mergeCell ref="AP52:AR52"/>
@@ -14721,6 +15648,7 @@
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="J56:P56"/>
+    <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="X25:AD25"/>
     <mergeCell ref="AG16:AI16"/>
@@ -14731,6 +15659,7 @@
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
     <mergeCell ref="BE19:BG19"/>
@@ -14753,15 +15682,16 @@
     <mergeCell ref="BB18:BD18"/>
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B58:D58"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE27 AE29:AE33 AE35:AE48 AE50:AE56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE27 AE29:AE33 AE35:AE48 AE50:AE56 AE58:AE59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG27 AG29:AG33 AG35:AG48 AG50:AG56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG27 AG29:AG33 AG35:AG48 AG50:AG56 AG58:AG59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV27 AV29:AV33 AV35:AV48 AV50:AV56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV27 AV29:AV33 AV35:AV48 AV50:AV56 AV58:AV59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
